--- a/Team-Data/2010-11/3-24-2010-11.xlsx
+++ b/Team-Data/2010-11/3-24-2010-11.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.549</v>
+        <v>0.556</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J2" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L2" t="n">
         <v>6.4</v>
@@ -691,22 +758,22 @@
         <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O2" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P2" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
         <v>9.4</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T2" t="n">
         <v>39.5</v>
@@ -727,28 +794,28 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF2" t="n">
         <v>12</v>
       </c>
-      <c r="AF2" t="n">
-        <v>13</v>
-      </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>28</v>
@@ -760,16 +827,16 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL2" t="n">
         <v>13</v>
       </c>
-      <c r="AL2" t="n">
-        <v>14</v>
-      </c>
       <c r="AM2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -778,7 +845,7 @@
         <v>29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
@@ -790,19 +857,19 @@
         <v>26</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -811,7 +878,7 @@
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>0.721</v>
+        <v>0.714</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K3" t="n">
         <v>0.487</v>
@@ -873,7 +940,7 @@
         <v>13.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O3" t="n">
         <v>17.7</v>
@@ -882,13 +949,13 @@
         <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
         <v>39</v>
@@ -897,13 +964,13 @@
         <v>23.8</v>
       </c>
       <c r="V3" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
         <v>4.4</v>
@@ -915,13 +982,13 @@
         <v>20.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>4</v>
@@ -930,13 +997,13 @@
         <v>3</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,16 +1018,16 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -972,22 +1039,22 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
         <v>23</v>
@@ -996,7 +1063,7 @@
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>0.406</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
@@ -1043,10 +1110,10 @@
         <v>34.6</v>
       </c>
       <c r="J4" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
@@ -1055,7 +1122,7 @@
         <v>15.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
@@ -1064,22 +1131,22 @@
         <v>25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.754</v>
       </c>
       <c r="R4" t="n">
         <v>10.7</v>
       </c>
       <c r="S4" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T4" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U4" t="n">
         <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
         <v>6.4</v>
@@ -1088,22 +1155,22 @@
         <v>5.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
         <v>20.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1127,13 +1194,13 @@
         <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM4" t="n">
         <v>26</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
@@ -1148,22 +1215,22 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>18</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,13 +1239,13 @@
         <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" t="n">
         <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.739</v>
+        <v>0.729</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K5" t="n">
         <v>0.46</v>
@@ -1234,19 +1301,19 @@
         <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P5" t="n">
         <v>24.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
@@ -1255,7 +1322,7 @@
         <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U5" t="n">
         <v>22</v>
@@ -1273,19 +1340,19 @@
         <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1297,19 +1364,19 @@
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>17</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>16</v>
       </c>
-      <c r="AK5" t="n">
-        <v>15</v>
-      </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM5" t="n">
         <v>17</v>
@@ -1318,7 +1385,7 @@
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>13</v>
@@ -1327,10 +1394,10 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
@@ -1339,25 +1406,25 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
         <v>10</v>
       </c>
       <c r="BA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB5" t="n">
         <v>20</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>19</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
         <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>0.174</v>
+        <v>0.186</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
@@ -1416,16 +1483,16 @@
         <v>6.2</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
         <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.743</v>
@@ -1440,7 +1507,7 @@
         <v>40.3</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V6" t="n">
         <v>14.4</v>
@@ -1458,16 +1525,16 @@
         <v>19.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
         <v>94.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>-10.7</v>
+        <v>-10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>30</v>
@@ -1479,7 +1546,7 @@
         <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>28</v>
@@ -1497,10 +1564,10 @@
         <v>14</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
@@ -1521,7 +1588,7 @@
         <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
         <v>23</v>
@@ -1539,7 +1606,7 @@
         <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -1589,25 +1656,25 @@
         <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="N7" t="n">
         <v>0.371</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P7" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0.784</v>
@@ -1622,7 +1689,7 @@
         <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V7" t="n">
         <v>13.7</v>
@@ -1646,13 +1713,13 @@
         <v>100.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>5</v>
@@ -1685,7 +1752,7 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.592</v>
+        <v>0.597</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1774,7 +1841,7 @@
         <v>80.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L8" t="n">
         <v>8.1</v>
@@ -1783,16 +1850,16 @@
         <v>20.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="O8" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="P8" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R8" t="n">
         <v>9.5</v>
@@ -1801,7 +1868,7 @@
         <v>32.3</v>
       </c>
       <c r="T8" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
         <v>21.9</v>
@@ -1813,22 +1880,22 @@
         <v>7.2</v>
       </c>
       <c r="X8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.5</v>
+        <v>107.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1846,7 +1913,7 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -1861,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1873,10 +1940,10 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -1888,16 +1955,16 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
         <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>0.357</v>
+        <v>0.352</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1965,16 +2032,16 @@
         <v>15.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O9" t="n">
         <v>16.4</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="R9" t="n">
         <v>11.3</v>
@@ -1989,7 +2056,7 @@
         <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
@@ -2013,7 +2080,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2028,7 +2095,7 @@
         <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ9" t="n">
         <v>14</v>
@@ -2037,7 +2104,7 @@
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>21</v>
@@ -2049,16 +2116,16 @@
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
         <v>30</v>
@@ -2082,13 +2149,13 @@
         <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB9" t="n">
         <v>24</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>0.408</v>
+        <v>0.417</v>
       </c>
       <c r="H10" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L10" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="N10" t="n">
         <v>0.39</v>
       </c>
       <c r="O10" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
@@ -2168,7 +2235,7 @@
         <v>40.2</v>
       </c>
       <c r="U10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2183,16 +2250,16 @@
         <v>4.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
         <v>18.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>102.3</v>
+        <v>102.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2201,7 +2268,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
@@ -2210,13 +2277,13 @@
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>5</v>
@@ -2225,7 +2292,7 @@
         <v>6</v>
       </c>
       <c r="AN10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="n">
         <v>30</v>
@@ -2234,10 +2301,10 @@
         <v>30</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>27</v>
@@ -2246,10 +2313,10 @@
         <v>25</v>
       </c>
       <c r="AU10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
@@ -2258,10 +2325,10 @@
         <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
         <v>38</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>0.543</v>
+        <v>0.528</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,46 +2384,46 @@
         <v>38.5</v>
       </c>
       <c r="J11" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N11" t="n">
         <v>0.367</v>
       </c>
       <c r="O11" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="P11" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.794</v>
+        <v>0.797</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S11" t="n">
         <v>30.9</v>
       </c>
       <c r="T11" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U11" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V11" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>4.7</v>
@@ -2365,37 +2432,37 @@
         <v>5.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.4</v>
+        <v>105.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
         <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
@@ -2407,19 +2474,19 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" t="n">
         <v>5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>13</v>
@@ -2437,22 +2504,22 @@
         <v>16</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
         <v>23</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
         <v>7</v>
       </c>
       <c r="BB11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
         <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>0.451</v>
+        <v>0.444</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J12" t="n">
         <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>7.2</v>
@@ -2511,31 +2578,31 @@
         <v>20.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O12" t="n">
         <v>19.5</v>
       </c>
       <c r="P12" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2547,16 +2614,16 @@
         <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
         <v>21.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2613,7 +2680,7 @@
         <v>29</v>
       </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>21</v>
@@ -2622,7 +2689,7 @@
         <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>22</v>
@@ -2631,10 +2698,10 @@
         <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" t="n">
         <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>0.394</v>
+        <v>0.389</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2693,7 +2760,7 @@
         <v>18.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
         <v>19.2</v>
@@ -2702,19 +2769,19 @@
         <v>27</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R13" t="n">
         <v>11.6</v>
       </c>
       <c r="S13" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T13" t="n">
         <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V13" t="n">
         <v>16.2</v>
@@ -2726,7 +2793,7 @@
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z13" t="n">
         <v>21.1</v>
@@ -2735,10 +2802,10 @@
         <v>22.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -2771,7 +2838,7 @@
         <v>11</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
@@ -2783,16 +2850,16 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV13" t="n">
         <v>29</v>
@@ -2801,16 +2868,16 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.714</v>
+        <v>0.718</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
         <v>18.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O14" t="n">
         <v>18.6</v>
@@ -2884,13 +2951,13 @@
         <v>23.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R14" t="n">
         <v>12.2</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
         <v>43.9</v>
@@ -2899,43 +2966,43 @@
         <v>22.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>7.4</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
         <v>3</v>
       </c>
-      <c r="AF14" t="n">
-        <v>4</v>
-      </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI14" t="n">
         <v>6</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>13</v>
@@ -2965,7 +3032,7 @@
         <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>9</v>
@@ -2992,10 +3059,10 @@
         <v>2</v>
       </c>
       <c r="BA14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" t="n">
         <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
@@ -3045,7 +3112,7 @@
         <v>39</v>
       </c>
       <c r="J15" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.468</v>
@@ -3054,10 +3121,10 @@
         <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="O15" t="n">
         <v>18.2</v>
@@ -3078,22 +3145,22 @@
         <v>41</v>
       </c>
       <c r="U15" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V15" t="n">
         <v>13.9</v>
       </c>
       <c r="W15" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="n">
         <v>21.3</v>
@@ -3102,19 +3169,19 @@
         <v>99.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>7</v>
@@ -3135,16 +3202,16 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
         <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
@@ -3156,7 +3223,7 @@
         <v>17</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
         <v>13</v>
@@ -3174,13 +3241,13 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.696</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J16" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L16" t="n">
         <v>6.6</v>
@@ -3239,7 +3306,7 @@
         <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O16" t="n">
         <v>21.5</v>
@@ -3248,25 +3315,25 @@
         <v>27.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R16" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S16" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X16" t="n">
         <v>5.4</v>
@@ -3278,31 +3345,31 @@
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>101.9</v>
+        <v>101.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" t="n">
         <v>6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>5</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3314,10 +3381,10 @@
         <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3326,28 +3393,28 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>28</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>24</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
@@ -3359,7 +3426,7 @@
         <v>5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>0.406</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>34.1</v>
       </c>
       <c r="J17" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K17" t="n">
         <v>0.427</v>
@@ -3427,16 +3494,16 @@
         <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R17" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
         <v>41.1</v>
@@ -3448,7 +3515,7 @@
         <v>13.6</v>
       </c>
       <c r="W17" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X17" t="n">
         <v>4.9</v>
@@ -3457,10 +3524,10 @@
         <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB17" t="n">
         <v>91.40000000000001</v>
@@ -3469,7 +3536,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3499,13 +3566,13 @@
         <v>18</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ17" t="n">
         <v>23</v>
@@ -3514,7 +3581,7 @@
         <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
         <v>16</v>
@@ -3526,25 +3593,25 @@
         <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
         <v>15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -3588,10 +3655,10 @@
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="K18" t="n">
         <v>0.438</v>
@@ -3606,10 +3673,10 @@
         <v>0.372</v>
       </c>
       <c r="O18" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.767</v>
@@ -3621,7 +3688,7 @@
         <v>31.4</v>
       </c>
       <c r="T18" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="U18" t="n">
         <v>20.3</v>
@@ -3633,28 +3700,28 @@
         <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y18" t="n">
         <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>101.1</v>
+        <v>101.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>29</v>
@@ -3663,10 +3730,10 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3708,7 +3775,7 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -3717,10 +3784,10 @@
         <v>24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -3755,37 +3822,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.319</v>
+        <v>0.329</v>
       </c>
       <c r="H19" t="n">
         <v>48.9</v>
       </c>
       <c r="I19" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J19" t="n">
         <v>80.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
         <v>18</v>
@@ -3794,25 +3861,25 @@
         <v>23.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R19" t="n">
         <v>11.3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T19" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U19" t="n">
         <v>20.7</v>
       </c>
       <c r="V19" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
@@ -3821,19 +3888,19 @@
         <v>4.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA19" t="n">
         <v>20.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3851,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3863,10 +3930,10 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
@@ -3875,10 +3942,10 @@
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
         <v>14</v>
@@ -3887,7 +3954,7 @@
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
@@ -3899,7 +3966,7 @@
         <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -3952,40 +4019,40 @@
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J20" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="T20" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U20" t="n">
         <v>20.5</v>
@@ -3997,28 +4064,28 @@
         <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC20" t="n">
         <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4027,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4036,25 +4103,25 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
       </c>
       <c r="AM20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>25</v>
@@ -4066,31 +4133,31 @@
         <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ20" t="n">
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
         <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
@@ -4140,7 +4207,7 @@
         <v>83.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L21" t="n">
         <v>9.300000000000001</v>
@@ -4149,13 +4216,13 @@
         <v>24.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O21" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q21" t="n">
         <v>0.8070000000000001</v>
@@ -4164,46 +4231,46 @@
         <v>10.3</v>
       </c>
       <c r="S21" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X21" t="n">
         <v>5.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z21" t="n">
         <v>21.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
         <v>18</v>
@@ -4215,7 +4282,7 @@
         <v>7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK21" t="n">
         <v>18</v>
@@ -4230,7 +4297,7 @@
         <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP21" t="n">
         <v>9</v>
@@ -4257,7 +4324,7 @@
         <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY21" t="n">
         <v>11</v>
@@ -4266,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="BA21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H22" t="n">
         <v>48.8</v>
@@ -4319,10 +4386,10 @@
         <v>37.2</v>
       </c>
       <c r="J22" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L22" t="n">
         <v>5.9</v>
@@ -4331,34 +4398,34 @@
         <v>16.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.825</v>
+        <v>0.824</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S22" t="n">
         <v>31.6</v>
       </c>
       <c r="T22" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
         <v>13.8</v>
       </c>
       <c r="W22" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X22" t="n">
         <v>5.7</v>
@@ -4367,19 +4434,19 @@
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB22" t="n">
         <v>104.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -4397,13 +4464,13 @@
         <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM22" t="n">
         <v>19</v>
@@ -4427,10 +4494,10 @@
         <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4442,10 +4509,10 @@
         <v>5</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23" t="n">
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.634</v>
+        <v>0.639</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L23" t="n">
         <v>9.4</v>
@@ -4513,25 +4580,25 @@
         <v>25.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O23" t="n">
         <v>17.8</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.695</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="T23" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U23" t="n">
         <v>20.1</v>
@@ -4552,13 +4619,13 @@
         <v>20.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,13 +4643,13 @@
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,13 +4658,13 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,10 +4673,10 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="n">
         <v>25</v>
@@ -4618,10 +4685,10 @@
         <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY23" t="n">
         <v>3</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E24" t="n">
         <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>0.529</v>
+        <v>0.521</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
@@ -4686,7 +4753,7 @@
         <v>82.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L24" t="n">
         <v>5.5</v>
@@ -4698,10 +4765,10 @@
         <v>0.361</v>
       </c>
       <c r="O24" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P24" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
         <v>0.771</v>
@@ -4713,13 +4780,13 @@
         <v>31.9</v>
       </c>
       <c r="T24" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U24" t="n">
         <v>22.6</v>
       </c>
       <c r="V24" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W24" t="n">
         <v>7.5</v>
@@ -4737,19 +4804,19 @@
         <v>18.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
@@ -4764,22 +4831,22 @@
         <v>12</v>
       </c>
       <c r="AK24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
         <v>14</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ24" t="n">
         <v>12</v>
@@ -4791,31 +4858,31 @@
         <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY24" t="n">
         <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.515</v>
+        <v>0.514</v>
       </c>
       <c r="H25" t="n">
         <v>48.9</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J25" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K25" t="n">
         <v>0.47</v>
@@ -4877,10 +4944,10 @@
         <v>23.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
         <v>23.6</v>
@@ -4892,13 +4959,13 @@
         <v>10</v>
       </c>
       <c r="S25" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V25" t="n">
         <v>14.3</v>
@@ -4913,25 +4980,25 @@
         <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
         <v>16</v>
@@ -4940,10 +5007,10 @@
         <v>2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4958,7 +5025,7 @@
         <v>4</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>20</v>
@@ -4976,28 +5043,28 @@
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
         <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -5029,64 +5096,64 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
         <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.447</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.343</v>
+        <v>0.346</v>
       </c>
       <c r="O26" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="P26" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.801</v>
+        <v>0.8</v>
       </c>
       <c r="R26" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S26" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="T26" t="n">
-        <v>39.1</v>
+        <v>39.4</v>
       </c>
       <c r="U26" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V26" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X26" t="n">
         <v>4.6</v>
@@ -5095,22 +5162,22 @@
         <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
         <v>10</v>
@@ -5125,34 +5192,34 @@
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
         <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5167,22 +5234,22 @@
         <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>0.246</v>
+        <v>0.257</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5232,22 +5299,22 @@
         <v>84.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N27" t="n">
         <v>0.341</v>
       </c>
       <c r="O27" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.731</v>
@@ -5262,7 +5329,7 @@
         <v>43.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
         <v>16.2</v>
@@ -5280,16 +5347,16 @@
         <v>22.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.8</v>
+        <v>-5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5301,13 +5368,13 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
@@ -5316,19 +5383,19 @@
         <v>25</v>
       </c>
       <c r="AM27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AN27" t="n">
         <v>25</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -5337,7 +5404,7 @@
         <v>19</v>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5346,22 +5413,22 @@
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY27" t="n">
         <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>0.803</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5423,34 +5490,34 @@
         <v>21</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="O28" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P28" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R28" t="n">
         <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T28" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V28" t="n">
         <v>13.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.7</v>
@@ -5465,13 +5532,13 @@
         <v>20.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.4</v>
+        <v>103.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5486,10 +5553,10 @@
         <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5510,7 +5577,7 @@
         <v>14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>23</v>
@@ -5519,7 +5586,7 @@
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5528,7 +5595,7 @@
         <v>7</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX28" t="n">
         <v>19</v>
@@ -5546,7 +5613,7 @@
         <v>6</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -5575,34 +5642,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
-        <v>0.286</v>
+        <v>0.282</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L29" t="n">
         <v>4.3</v>
       </c>
       <c r="M29" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N29" t="n">
         <v>0.314</v>
@@ -5623,37 +5690,37 @@
         <v>28.7</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U29" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W29" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z29" t="n">
         <v>22.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>-5.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
         <v>4</v>
@@ -5674,7 +5741,7 @@
         <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="n">
         <v>29</v>
@@ -5689,13 +5756,13 @@
         <v>19</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
         <v>19</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
@@ -5704,7 +5771,7 @@
         <v>24</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>22</v>
@@ -5719,13 +5786,13 @@
         <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA29" t="n">
         <v>26</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -5757,82 +5824,82 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
         <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.507</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>37.7</v>
+        <v>37.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M30" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.345</v>
       </c>
       <c r="O30" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="P30" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R30" t="n">
         <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T30" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="U30" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V30" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="W30" t="n">
         <v>7.7</v>
       </c>
       <c r="X30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y30" t="n">
         <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>100.6</v>
+        <v>100.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5847,16 +5914,16 @@
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>22</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR30" t="n">
         <v>16</v>
@@ -5889,13 +5956,13 @@
         <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
@@ -5904,13 +5971,13 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
         <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G31" t="n">
-        <v>0.246</v>
+        <v>0.243</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J31" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -5969,37 +6036,37 @@
         <v>14.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.334</v>
+        <v>0.332</v>
       </c>
       <c r="O31" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P31" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T31" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U31" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V31" t="n">
         <v>15.4</v>
       </c>
       <c r="W31" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y31" t="n">
         <v>4.8</v>
@@ -6011,22 +6078,22 @@
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.8</v>
+        <v>-8.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6053,13 +6120,13 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
         <v>25</v>
@@ -6071,7 +6138,7 @@
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
@@ -6080,16 +6147,16 @@
         <v>1</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-24-2010-11</t>
+          <t>2011-03-24</t>
         </is>
       </c>
     </row>
